--- a/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>SY</t>
   </si>
@@ -656,340 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>56900</v>
+        <v>53600</v>
       </c>
       <c r="E8" s="3">
-        <v>42800</v>
+        <v>57300</v>
       </c>
       <c r="F8" s="3">
+        <v>43100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>45200</v>
+      </c>
+      <c r="H8" s="3">
         <v>44900</v>
       </c>
-      <c r="G8" s="3">
-        <v>44600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>42700</v>
-      </c>
       <c r="I8" s="3">
-        <v>41500</v>
+        <v>43000</v>
       </c>
       <c r="J8" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K8" s="3">
         <v>62100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>64200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>59100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>53000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>48400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>55200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>43500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>20800</v>
+        <v>19800</v>
       </c>
       <c r="E9" s="3">
-        <v>15700</v>
+        <v>20900</v>
       </c>
       <c r="F9" s="3">
-        <v>12200</v>
+        <v>15800</v>
       </c>
       <c r="G9" s="3">
-        <v>13000</v>
+        <v>12300</v>
       </c>
       <c r="H9" s="3">
-        <v>14400</v>
+        <v>13100</v>
       </c>
       <c r="I9" s="3">
-        <v>14700</v>
+        <v>14500</v>
       </c>
       <c r="J9" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K9" s="3">
         <v>17500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>36100</v>
+        <v>33700</v>
       </c>
       <c r="E10" s="3">
-        <v>27100</v>
+        <v>36400</v>
       </c>
       <c r="F10" s="3">
-        <v>32700</v>
+        <v>27300</v>
       </c>
       <c r="G10" s="3">
-        <v>31700</v>
+        <v>32900</v>
       </c>
       <c r="H10" s="3">
-        <v>28300</v>
+        <v>31900</v>
       </c>
       <c r="I10" s="3">
-        <v>26700</v>
+        <v>28400</v>
       </c>
       <c r="J10" s="3">
+        <v>26900</v>
+      </c>
+      <c r="K10" s="3">
         <v>44500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>55900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>44100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>50200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>44900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>40900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>35900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1029,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E12" s="3">
         <v>7200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>10300</v>
+      </c>
+      <c r="N12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>9900</v>
+      </c>
+      <c r="P12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q12" s="3">
         <v>7700</v>
       </c>
-      <c r="F12" s="3">
-        <v>5700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>8700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>10900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>9300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>10300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>9900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>9300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>7700</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,59 +1181,62 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
         <v>9100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1229,8 +1249,8 @@
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1238,8 +1258,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>59800</v>
+        <v>53800</v>
       </c>
       <c r="E17" s="3">
-        <v>47400</v>
+        <v>60200</v>
       </c>
       <c r="F17" s="3">
-        <v>41500</v>
+        <v>47800</v>
       </c>
       <c r="G17" s="3">
-        <v>46800</v>
+        <v>41800</v>
       </c>
       <c r="H17" s="3">
-        <v>48500</v>
+        <v>47100</v>
       </c>
       <c r="I17" s="3">
-        <v>52200</v>
+        <v>48800</v>
       </c>
       <c r="J17" s="3">
+        <v>52600</v>
+      </c>
+      <c r="K17" s="3">
         <v>68900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>61100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>60300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>41900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5800</v>
       </c>
-      <c r="I18" s="3">
-        <v>-10700</v>
-      </c>
       <c r="J18" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1513,8 +1546,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1522,73 +1556,76 @@
         <v>2600</v>
       </c>
       <c r="E20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1400</v>
       </c>
       <c r="M20" s="3">
         <v>1400</v>
       </c>
       <c r="N20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O20" s="3">
         <v>2900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>2200</v>
       </c>
       <c r="P20" s="3">
         <v>2200</v>
       </c>
       <c r="Q20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1661,8 +1698,11 @@
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1735,156 +1775,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
-        <v>-1600</v>
-      </c>
       <c r="F27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G27" s="3">
         <v>4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4500</v>
       </c>
-      <c r="I27" s="3">
-        <v>-9200</v>
-      </c>
       <c r="J27" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2468,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2410,147 +2480,153 @@
         <v>-2600</v>
       </c>
       <c r="E32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1400</v>
       </c>
       <c r="M32" s="3">
         <v>-1400</v>
       </c>
       <c r="N32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-2200</v>
       </c>
       <c r="P32" s="3">
         <v>-2200</v>
       </c>
       <c r="Q32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
-        <v>-1600</v>
-      </c>
       <c r="F33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G33" s="3">
         <v>4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4500</v>
       </c>
-      <c r="I33" s="3">
-        <v>-9200</v>
-      </c>
       <c r="J33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
-        <v>-1600</v>
-      </c>
       <c r="F35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G35" s="3">
         <v>4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4500</v>
       </c>
-      <c r="I35" s="3">
-        <v>-9200</v>
-      </c>
       <c r="J35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,68 +2918,69 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>104800</v>
+        <v>61000</v>
       </c>
       <c r="E41" s="3">
-        <v>112700</v>
+        <v>105500</v>
       </c>
       <c r="F41" s="3">
-        <v>95900</v>
+        <v>113400</v>
       </c>
       <c r="G41" s="3">
-        <v>98500</v>
+        <v>96500</v>
       </c>
       <c r="H41" s="3">
-        <v>203200</v>
+        <v>99200</v>
       </c>
       <c r="I41" s="3">
-        <v>216000</v>
+        <v>204600</v>
       </c>
       <c r="J41" s="3">
+        <v>217500</v>
+      </c>
+      <c r="K41" s="3">
         <v>183900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>163300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>139800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>156900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>232000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>144600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>136200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>94000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>169200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>108000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2906,68 +2993,71 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>105300</v>
+        <v>132200</v>
       </c>
       <c r="E42" s="3">
-        <v>89500</v>
+        <v>106000</v>
       </c>
       <c r="F42" s="3">
-        <v>121000</v>
+        <v>90100</v>
       </c>
       <c r="G42" s="3">
-        <v>125500</v>
+        <v>121800</v>
       </c>
       <c r="H42" s="3">
-        <v>15300</v>
+        <v>126300</v>
       </c>
       <c r="I42" s="3">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="J42" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K42" s="3">
         <v>56500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>154200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>230000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>212600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>329000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>190600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>288200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>299200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>331800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>238000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>85300</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2980,68 +3070,71 @@
       <c r="Z42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E43" s="3">
         <v>13200</v>
       </c>
-      <c r="E43" s="3">
-        <v>11000</v>
-      </c>
       <c r="F43" s="3">
-        <v>11600</v>
+        <v>11100</v>
       </c>
       <c r="G43" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>12500</v>
+      </c>
+      <c r="I43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="L43" s="3">
+        <v>15500</v>
+      </c>
+      <c r="M43" s="3">
+        <v>14000</v>
+      </c>
+      <c r="N43" s="3">
         <v>12400</v>
       </c>
-      <c r="H43" s="3">
-        <v>11700</v>
-      </c>
-      <c r="I43" s="3">
-        <v>12100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>12100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>15500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>14000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>12400</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8200</v>
-      </c>
-      <c r="R43" s="3">
-        <v>7000</v>
       </c>
       <c r="S43" s="3">
         <v>7000</v>
       </c>
       <c r="T43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="U43" s="3">
         <v>4300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3054,38 +3147,41 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="E44" s="3">
-        <v>16500</v>
+        <v>17100</v>
       </c>
       <c r="F44" s="3">
         <v>16600</v>
       </c>
       <c r="G44" s="3">
-        <v>14500</v>
+        <v>16700</v>
       </c>
       <c r="H44" s="3">
-        <v>13100</v>
+        <v>14600</v>
       </c>
       <c r="I44" s="3">
-        <v>12300</v>
+        <v>13200</v>
       </c>
       <c r="J44" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K44" s="3">
         <v>12700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3101,8 +3197,8 @@
       <c r="Q44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3128,68 +3224,71 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>23200</v>
+        <v>27500</v>
       </c>
       <c r="E45" s="3">
-        <v>19900</v>
+        <v>23300</v>
       </c>
       <c r="F45" s="3">
-        <v>19600</v>
+        <v>20000</v>
       </c>
       <c r="G45" s="3">
-        <v>22900</v>
+        <v>19700</v>
       </c>
       <c r="H45" s="3">
-        <v>19800</v>
+        <v>23000</v>
       </c>
       <c r="I45" s="3">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="J45" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K45" s="3">
         <v>14800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>17100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>13000</v>
       </c>
       <c r="R45" s="3">
         <v>13000</v>
       </c>
       <c r="S45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="T45" s="3">
         <v>13500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8700</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3202,68 +3301,71 @@
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>263400</v>
+        <v>252800</v>
       </c>
       <c r="E46" s="3">
-        <v>249500</v>
+        <v>265200</v>
       </c>
       <c r="F46" s="3">
-        <v>264700</v>
+        <v>251200</v>
       </c>
       <c r="G46" s="3">
-        <v>273900</v>
+        <v>266500</v>
       </c>
       <c r="H46" s="3">
-        <v>263100</v>
+        <v>275700</v>
       </c>
       <c r="I46" s="3">
-        <v>269700</v>
+        <v>264900</v>
       </c>
       <c r="J46" s="3">
+        <v>271600</v>
+      </c>
+      <c r="K46" s="3">
         <v>279900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>302900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>348900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>394800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>389200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>431900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>441900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>453900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>455300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>446200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>423400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>206300</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3276,68 +3378,71 @@
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>34800</v>
+        <v>35100</v>
       </c>
       <c r="E47" s="3">
-        <v>33700</v>
+        <v>35000</v>
       </c>
       <c r="F47" s="3">
-        <v>31500</v>
+        <v>33900</v>
       </c>
       <c r="G47" s="3">
-        <v>32300</v>
+        <v>31700</v>
       </c>
       <c r="H47" s="3">
-        <v>34700</v>
+        <v>32500</v>
       </c>
       <c r="I47" s="3">
-        <v>34700</v>
+        <v>34900</v>
       </c>
       <c r="J47" s="3">
         <v>34900</v>
       </c>
       <c r="K47" s="3">
+        <v>34900</v>
+      </c>
+      <c r="L47" s="3">
         <v>36000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>25000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>23100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2300</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3350,68 +3455,71 @@
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22600</v>
+        <v>20700</v>
       </c>
       <c r="E48" s="3">
-        <v>23300</v>
+        <v>22700</v>
       </c>
       <c r="F48" s="3">
-        <v>24700</v>
+        <v>23500</v>
       </c>
       <c r="G48" s="3">
-        <v>25800</v>
+        <v>24900</v>
       </c>
       <c r="H48" s="3">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="I48" s="3">
-        <v>29200</v>
+        <v>28200</v>
       </c>
       <c r="J48" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K48" s="3">
         <v>30400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3424,56 +3532,59 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>96300</v>
+        <v>96200</v>
       </c>
       <c r="E49" s="3">
-        <v>97200</v>
+        <v>97000</v>
       </c>
       <c r="F49" s="3">
-        <v>98000</v>
+        <v>97800</v>
       </c>
       <c r="G49" s="3">
-        <v>98900</v>
+        <v>98700</v>
       </c>
       <c r="H49" s="3">
-        <v>99800</v>
+        <v>99600</v>
       </c>
       <c r="I49" s="3">
-        <v>100600</v>
+        <v>100500</v>
       </c>
       <c r="J49" s="3">
+        <v>101300</v>
+      </c>
+      <c r="K49" s="3">
         <v>101400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>107500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6900</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3489,8 +3600,8 @@
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,68 +3763,71 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>19900</v>
+        <v>30700</v>
       </c>
       <c r="E52" s="3">
-        <v>23600</v>
+        <v>20000</v>
       </c>
       <c r="F52" s="3">
-        <v>22600</v>
+        <v>23700</v>
       </c>
       <c r="G52" s="3">
-        <v>27100</v>
+        <v>22800</v>
       </c>
       <c r="H52" s="3">
-        <v>21200</v>
+        <v>27300</v>
       </c>
       <c r="I52" s="3">
-        <v>14500</v>
+        <v>21400</v>
       </c>
       <c r="J52" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K52" s="3">
         <v>13200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7500</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,68 +3917,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>436900</v>
+        <v>435500</v>
       </c>
       <c r="E54" s="3">
-        <v>427300</v>
+        <v>439900</v>
       </c>
       <c r="F54" s="3">
-        <v>441600</v>
+        <v>430200</v>
       </c>
       <c r="G54" s="3">
-        <v>458000</v>
+        <v>444600</v>
       </c>
       <c r="H54" s="3">
-        <v>446800</v>
+        <v>461100</v>
       </c>
       <c r="I54" s="3">
-        <v>448800</v>
+        <v>449800</v>
       </c>
       <c r="J54" s="3">
+        <v>451800</v>
+      </c>
+      <c r="K54" s="3">
         <v>459900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>511200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>442400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>471200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>458200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>477500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>486800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>503400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>497300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>487300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>462900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>242700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3868,8 +3994,11 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,8 +4054,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3933,14 +4064,14 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
@@ -3948,13 +4079,13 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
@@ -3963,28 +4094,28 @@
         <v>300</v>
       </c>
       <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>400</v>
       </c>
       <c r="S57" s="3">
+        <v>400</v>
+      </c>
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>16</v>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>16</v>
@@ -3998,8 +4129,11 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4072,68 +4206,71 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>81300</v>
+        <v>77500</v>
       </c>
       <c r="E59" s="3">
-        <v>71500</v>
+        <v>81800</v>
       </c>
       <c r="F59" s="3">
-        <v>73500</v>
+        <v>72000</v>
       </c>
       <c r="G59" s="3">
-        <v>94800</v>
+        <v>74000</v>
       </c>
       <c r="H59" s="3">
-        <v>91300</v>
+        <v>95500</v>
       </c>
       <c r="I59" s="3">
-        <v>96200</v>
+        <v>91900</v>
       </c>
       <c r="J59" s="3">
+        <v>96800</v>
+      </c>
+      <c r="K59" s="3">
         <v>98300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>135800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>84400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>82800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>79100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>73200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>64100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>71400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>68700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>61900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>57400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4146,68 +4283,71 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>81300</v>
+        <v>77600</v>
       </c>
       <c r="E60" s="3">
-        <v>71500</v>
+        <v>81900</v>
       </c>
       <c r="F60" s="3">
-        <v>74300</v>
+        <v>72000</v>
       </c>
       <c r="G60" s="3">
-        <v>94800</v>
+        <v>74800</v>
       </c>
       <c r="H60" s="3">
-        <v>91300</v>
+        <v>95500</v>
       </c>
       <c r="I60" s="3">
-        <v>96200</v>
+        <v>91900</v>
       </c>
       <c r="J60" s="3">
+        <v>96800</v>
+      </c>
+      <c r="K60" s="3">
         <v>98400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>135900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>83100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>79500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>74400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>73600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>64500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>71800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>69200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>62600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>57400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4220,8 +4360,11 @@
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4294,68 +4437,71 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E62" s="3">
         <v>4900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7200</v>
       </c>
-      <c r="G62" s="3">
-        <v>9100</v>
-      </c>
       <c r="H62" s="3">
-        <v>10800</v>
+        <v>9200</v>
       </c>
       <c r="I62" s="3">
-        <v>12300</v>
+        <v>10900</v>
       </c>
       <c r="J62" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K62" s="3">
         <v>13900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,68 +4745,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>102000</v>
+        <v>98200</v>
       </c>
       <c r="E66" s="3">
-        <v>93300</v>
+        <v>102700</v>
       </c>
       <c r="F66" s="3">
-        <v>96600</v>
+        <v>94000</v>
       </c>
       <c r="G66" s="3">
-        <v>113700</v>
+        <v>97300</v>
       </c>
       <c r="H66" s="3">
-        <v>111800</v>
+        <v>114400</v>
       </c>
       <c r="I66" s="3">
-        <v>118200</v>
+        <v>112600</v>
       </c>
       <c r="J66" s="3">
+        <v>119100</v>
+      </c>
+      <c r="K66" s="3">
         <v>122100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>99900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>96800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>91300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>84500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>89200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>83600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>79300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4897,11 +5065,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>218000</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,68 +5159,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-45900</v>
+        <v>-43600</v>
       </c>
       <c r="E72" s="3">
-        <v>-45500</v>
+        <v>-46200</v>
       </c>
       <c r="F72" s="3">
-        <v>-43900</v>
+        <v>-45800</v>
       </c>
       <c r="G72" s="3">
-        <v>-48200</v>
+        <v>-44200</v>
       </c>
       <c r="H72" s="3">
         <v>-48500</v>
       </c>
       <c r="I72" s="3">
-        <v>-44000</v>
+        <v>-48800</v>
       </c>
       <c r="J72" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-34800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-32800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-41500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-41600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-45000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-38300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-49100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-53500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-57700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5062,8 +5236,11 @@
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,68 +5467,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>334900</v>
+        <v>337300</v>
       </c>
       <c r="E76" s="3">
-        <v>333900</v>
+        <v>337200</v>
       </c>
       <c r="F76" s="3">
-        <v>344900</v>
+        <v>336200</v>
       </c>
       <c r="G76" s="3">
-        <v>344400</v>
+        <v>347300</v>
       </c>
       <c r="H76" s="3">
-        <v>335000</v>
+        <v>346700</v>
       </c>
       <c r="I76" s="3">
-        <v>330500</v>
+        <v>337300</v>
       </c>
       <c r="J76" s="3">
+        <v>332800</v>
+      </c>
+      <c r="K76" s="3">
         <v>337800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>347100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>342300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>371300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>361400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>386700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>395500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>418900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>406900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>398100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>379300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-54600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
-        <v>-1600</v>
-      </c>
       <c r="F81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G81" s="3">
         <v>4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4500</v>
       </c>
-      <c r="I81" s="3">
-        <v>-9200</v>
-      </c>
       <c r="J81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6271,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6131,8 +6348,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6608,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6455,8 +6685,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7022,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6853,8 +7099,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,8 +7176,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6999,6 +7251,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>SY</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>53600</v>
+        <v>54000</v>
       </c>
       <c r="E8" s="3">
-        <v>57300</v>
+        <v>53200</v>
       </c>
       <c r="F8" s="3">
-        <v>43100</v>
+        <v>56900</v>
       </c>
       <c r="G8" s="3">
-        <v>45200</v>
+        <v>42800</v>
       </c>
       <c r="H8" s="3">
         <v>44900</v>
       </c>
       <c r="I8" s="3">
-        <v>43000</v>
+        <v>44700</v>
       </c>
       <c r="J8" s="3">
+        <v>42700</v>
+      </c>
+      <c r="K8" s="3">
         <v>41700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>62100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>64200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>51600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>59100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>53000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>48400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>28800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>55200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>43500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>23600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19800</v>
+        <v>19000</v>
       </c>
       <c r="E9" s="3">
-        <v>20900</v>
+        <v>19700</v>
       </c>
       <c r="F9" s="3">
-        <v>15800</v>
+        <v>20800</v>
       </c>
       <c r="G9" s="3">
-        <v>12300</v>
+        <v>15700</v>
       </c>
       <c r="H9" s="3">
-        <v>13100</v>
+        <v>12200</v>
       </c>
       <c r="I9" s="3">
-        <v>14500</v>
+        <v>13000</v>
       </c>
       <c r="J9" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K9" s="3">
         <v>14800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>33700</v>
+        <v>34900</v>
       </c>
       <c r="E10" s="3">
-        <v>36400</v>
+        <v>33500</v>
       </c>
       <c r="F10" s="3">
-        <v>27300</v>
+        <v>36200</v>
       </c>
       <c r="G10" s="3">
-        <v>32900</v>
+        <v>27100</v>
       </c>
       <c r="H10" s="3">
-        <v>31900</v>
+        <v>32700</v>
       </c>
       <c r="I10" s="3">
-        <v>28400</v>
+        <v>31700</v>
       </c>
       <c r="J10" s="3">
+        <v>28300</v>
+      </c>
+      <c r="K10" s="3">
         <v>26900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>55900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>44100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>50200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>44900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>46100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>35900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>20200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E12" s="3">
         <v>7000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
       </c>
-      <c r="F12" s="3">
-        <v>7800</v>
-      </c>
       <c r="G12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H12" s="3">
         <v>5700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7200</v>
       </c>
-      <c r="I12" s="3">
-        <v>8800</v>
-      </c>
       <c r="J12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K12" s="3">
         <v>11000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1184,62 +1200,65 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3">
         <v>9100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1252,8 +1271,8 @@
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1261,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>53800</v>
+        <v>54700</v>
       </c>
       <c r="E17" s="3">
-        <v>60200</v>
+        <v>53500</v>
       </c>
       <c r="F17" s="3">
-        <v>47800</v>
+        <v>59800</v>
       </c>
       <c r="G17" s="3">
-        <v>41800</v>
+        <v>47500</v>
       </c>
       <c r="H17" s="3">
-        <v>47100</v>
+        <v>41600</v>
       </c>
       <c r="I17" s="3">
-        <v>48800</v>
+        <v>46800</v>
       </c>
       <c r="J17" s="3">
+        <v>48500</v>
+      </c>
+      <c r="K17" s="3">
         <v>52600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>68900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>61100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>56000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>60300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>41900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1547,85 +1579,89 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2600</v>
+        <v>1900</v>
       </c>
       <c r="E20" s="3">
         <v>2600</v>
       </c>
       <c r="F20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1400</v>
       </c>
       <c r="N20" s="3">
         <v>1400</v>
       </c>
       <c r="O20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P20" s="3">
         <v>2900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2200</v>
       </c>
       <c r="Q20" s="3">
         <v>2200</v>
       </c>
       <c r="R20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1701,8 +1737,11 @@
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1778,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="E23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,8 +2057,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2018,153 +2069,159 @@
         <v>2700</v>
       </c>
       <c r="E26" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2600</v>
+        <v>-1900</v>
       </c>
       <c r="E32" s="3">
         <v>-2600</v>
       </c>
       <c r="F32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1400</v>
       </c>
       <c r="N32" s="3">
         <v>-1400</v>
       </c>
       <c r="O32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-2200</v>
       </c>
       <c r="Q32" s="3">
         <v>-2200</v>
       </c>
       <c r="R32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,71 +3004,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>61000</v>
+        <v>58900</v>
       </c>
       <c r="E41" s="3">
-        <v>105500</v>
+        <v>60600</v>
       </c>
       <c r="F41" s="3">
-        <v>113400</v>
+        <v>104800</v>
       </c>
       <c r="G41" s="3">
-        <v>96500</v>
+        <v>112700</v>
       </c>
       <c r="H41" s="3">
-        <v>99200</v>
+        <v>95900</v>
       </c>
       <c r="I41" s="3">
-        <v>204600</v>
+        <v>98600</v>
       </c>
       <c r="J41" s="3">
+        <v>203300</v>
+      </c>
+      <c r="K41" s="3">
         <v>217500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>183900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>163300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>139800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>156900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>81400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>232000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>144600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>136200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>94000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>169200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>108000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2996,71 +3082,74 @@
       <c r="AA41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>132200</v>
+        <v>124500</v>
       </c>
       <c r="E42" s="3">
-        <v>106000</v>
+        <v>131400</v>
       </c>
       <c r="F42" s="3">
-        <v>90100</v>
+        <v>105300</v>
       </c>
       <c r="G42" s="3">
-        <v>121800</v>
+        <v>89500</v>
       </c>
       <c r="H42" s="3">
-        <v>126300</v>
+        <v>121000</v>
       </c>
       <c r="I42" s="3">
+        <v>125500</v>
+      </c>
+      <c r="J42" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K42" s="3">
         <v>15400</v>
       </c>
-      <c r="J42" s="3">
-        <v>15400</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>56500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>154200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>230000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>212600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>329000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>190600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>288200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>299200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>331800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>238000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>85300</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3073,71 +3162,74 @@
       <c r="AA42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16100</v>
+        <v>12400</v>
       </c>
       <c r="E43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F43" s="3">
         <v>13200</v>
       </c>
-      <c r="F43" s="3">
-        <v>11100</v>
-      </c>
       <c r="G43" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J43" s="3">
         <v>11700</v>
       </c>
-      <c r="H43" s="3">
-        <v>12500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>11800</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8200</v>
-      </c>
-      <c r="S43" s="3">
-        <v>7000</v>
       </c>
       <c r="T43" s="3">
         <v>7000</v>
       </c>
       <c r="U43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="V43" s="3">
         <v>4300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3150,41 +3242,44 @@
       <c r="AA43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>16000</v>
+        <v>16400</v>
       </c>
       <c r="E44" s="3">
-        <v>17100</v>
+        <v>15900</v>
       </c>
       <c r="F44" s="3">
+        <v>17000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>16500</v>
+      </c>
+      <c r="H44" s="3">
         <v>16600</v>
       </c>
-      <c r="G44" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H44" s="3">
-        <v>14600</v>
-      </c>
       <c r="I44" s="3">
-        <v>13200</v>
+        <v>14500</v>
       </c>
       <c r="J44" s="3">
+        <v>13100</v>
+      </c>
+      <c r="K44" s="3">
         <v>12400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3200,8 +3295,8 @@
       <c r="R44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3227,71 +3322,74 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27500</v>
+        <v>25800</v>
       </c>
       <c r="E45" s="3">
-        <v>23300</v>
+        <v>27400</v>
       </c>
       <c r="F45" s="3">
-        <v>20000</v>
+        <v>23200</v>
       </c>
       <c r="G45" s="3">
-        <v>19700</v>
+        <v>19900</v>
       </c>
       <c r="H45" s="3">
-        <v>23000</v>
+        <v>19600</v>
       </c>
       <c r="I45" s="3">
-        <v>20000</v>
+        <v>22900</v>
       </c>
       <c r="J45" s="3">
+        <v>19800</v>
+      </c>
+      <c r="K45" s="3">
         <v>14100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>13000</v>
       </c>
       <c r="S45" s="3">
         <v>13000</v>
       </c>
       <c r="T45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="U45" s="3">
         <v>13500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8700</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3304,71 +3402,74 @@
       <c r="AA45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>252800</v>
+        <v>237900</v>
       </c>
       <c r="E46" s="3">
-        <v>265200</v>
+        <v>251200</v>
       </c>
       <c r="F46" s="3">
-        <v>251200</v>
+        <v>263500</v>
       </c>
       <c r="G46" s="3">
-        <v>266500</v>
+        <v>249600</v>
       </c>
       <c r="H46" s="3">
-        <v>275700</v>
+        <v>264800</v>
       </c>
       <c r="I46" s="3">
-        <v>264900</v>
+        <v>274000</v>
       </c>
       <c r="J46" s="3">
+        <v>263300</v>
+      </c>
+      <c r="K46" s="3">
         <v>271600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>279900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>302900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>348900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>394800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>389200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>431900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>441900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>453900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>455300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>446200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>423400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>206300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3381,71 +3482,74 @@
       <c r="AA46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>35100</v>
+        <v>36100</v>
       </c>
       <c r="E47" s="3">
-        <v>35000</v>
+        <v>34900</v>
       </c>
       <c r="F47" s="3">
-        <v>33900</v>
+        <v>34800</v>
       </c>
       <c r="G47" s="3">
-        <v>31700</v>
+        <v>33700</v>
       </c>
       <c r="H47" s="3">
-        <v>32500</v>
+        <v>31500</v>
       </c>
       <c r="I47" s="3">
-        <v>34900</v>
+        <v>32300</v>
       </c>
       <c r="J47" s="3">
-        <v>34900</v>
+        <v>34700</v>
       </c>
       <c r="K47" s="3">
         <v>34900</v>
       </c>
       <c r="L47" s="3">
+        <v>34900</v>
+      </c>
+      <c r="M47" s="3">
         <v>36000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>23100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2300</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3458,71 +3562,74 @@
       <c r="AA47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20700</v>
+        <v>32500</v>
       </c>
       <c r="E48" s="3">
-        <v>22700</v>
+        <v>20600</v>
       </c>
       <c r="F48" s="3">
-        <v>23500</v>
+        <v>22600</v>
       </c>
       <c r="G48" s="3">
-        <v>24900</v>
+        <v>23300</v>
       </c>
       <c r="H48" s="3">
-        <v>26000</v>
+        <v>24700</v>
       </c>
       <c r="I48" s="3">
-        <v>28200</v>
+        <v>25800</v>
       </c>
       <c r="J48" s="3">
+        <v>28100</v>
+      </c>
+      <c r="K48" s="3">
         <v>29400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3535,59 +3642,62 @@
       <c r="AA48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>96200</v>
+        <v>94800</v>
       </c>
       <c r="E49" s="3">
-        <v>97000</v>
+        <v>95600</v>
       </c>
       <c r="F49" s="3">
-        <v>97800</v>
+        <v>96400</v>
       </c>
       <c r="G49" s="3">
-        <v>98700</v>
+        <v>97200</v>
       </c>
       <c r="H49" s="3">
-        <v>99600</v>
+        <v>98100</v>
       </c>
       <c r="I49" s="3">
-        <v>100500</v>
+        <v>99000</v>
       </c>
       <c r="J49" s="3">
+        <v>99800</v>
+      </c>
+      <c r="K49" s="3">
         <v>101300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>101400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>107500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3603,8 +3713,8 @@
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,71 +3882,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>30700</v>
+        <v>42900</v>
       </c>
       <c r="E52" s="3">
-        <v>20000</v>
+        <v>30500</v>
       </c>
       <c r="F52" s="3">
-        <v>23700</v>
+        <v>19900</v>
       </c>
       <c r="G52" s="3">
-        <v>22800</v>
+        <v>23600</v>
       </c>
       <c r="H52" s="3">
-        <v>27300</v>
+        <v>22700</v>
       </c>
       <c r="I52" s="3">
-        <v>21400</v>
+        <v>27200</v>
       </c>
       <c r="J52" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,71 +4042,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>435500</v>
+        <v>444100</v>
       </c>
       <c r="E54" s="3">
-        <v>439900</v>
+        <v>432800</v>
       </c>
       <c r="F54" s="3">
-        <v>430200</v>
+        <v>437100</v>
       </c>
       <c r="G54" s="3">
-        <v>444600</v>
+        <v>427500</v>
       </c>
       <c r="H54" s="3">
-        <v>461100</v>
+        <v>441800</v>
       </c>
       <c r="I54" s="3">
-        <v>449800</v>
+        <v>458300</v>
       </c>
       <c r="J54" s="3">
+        <v>447100</v>
+      </c>
+      <c r="K54" s="3">
         <v>451800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>459900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>511200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>442400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>471200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>458200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>477500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>486800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>503400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>497300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>487300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>462900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>242700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,8 +4184,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4067,14 +4197,14 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
       <c r="I57" s="3">
         <v>0</v>
       </c>
@@ -4082,13 +4212,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>300</v>
@@ -4097,28 +4227,28 @@
         <v>300</v>
       </c>
       <c r="P57" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>16</v>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>16</v>
@@ -4132,31 +4262,34 @@
       <c r="AA57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>4100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4209,71 +4342,74 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>77500</v>
+        <v>70500</v>
       </c>
       <c r="E59" s="3">
-        <v>81800</v>
+        <v>77100</v>
       </c>
       <c r="F59" s="3">
-        <v>72000</v>
+        <v>81300</v>
       </c>
       <c r="G59" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>73500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>94900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>91400</v>
+      </c>
+      <c r="K59" s="3">
+        <v>96800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>98300</v>
+      </c>
+      <c r="M59" s="3">
+        <v>135800</v>
+      </c>
+      <c r="N59" s="3">
+        <v>84400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>82800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>79100</v>
+      </c>
+      <c r="Q59" s="3">
         <v>74000</v>
       </c>
-      <c r="H59" s="3">
-        <v>95500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>91900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>96800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>98300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>135800</v>
-      </c>
-      <c r="M59" s="3">
-        <v>84400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>82800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>79100</v>
-      </c>
-      <c r="P59" s="3">
-        <v>74000</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>73200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>64100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>68700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>61900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>57400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4286,71 +4422,74 @@
       <c r="AA59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>77600</v>
+        <v>74700</v>
       </c>
       <c r="E60" s="3">
-        <v>81900</v>
+        <v>77200</v>
       </c>
       <c r="F60" s="3">
-        <v>72000</v>
+        <v>81400</v>
       </c>
       <c r="G60" s="3">
-        <v>74800</v>
+        <v>71600</v>
       </c>
       <c r="H60" s="3">
-        <v>95500</v>
+        <v>74300</v>
       </c>
       <c r="I60" s="3">
-        <v>91900</v>
+        <v>94900</v>
       </c>
       <c r="J60" s="3">
+        <v>91400</v>
+      </c>
+      <c r="K60" s="3">
         <v>96800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>98400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>135900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>84700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>83100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>79500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>74400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>73600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>64500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>71800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>69200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>62600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>57400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4363,8 +4502,11 @@
       <c r="AA60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4440,71 +4582,74 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7200</v>
       </c>
-      <c r="H62" s="3">
-        <v>9200</v>
-      </c>
       <c r="I62" s="3">
-        <v>10900</v>
+        <v>9100</v>
       </c>
       <c r="J62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K62" s="3">
         <v>12400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,71 +4902,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>98200</v>
+        <v>106400</v>
       </c>
       <c r="E66" s="3">
-        <v>102700</v>
+        <v>97600</v>
       </c>
       <c r="F66" s="3">
-        <v>94000</v>
+        <v>102100</v>
       </c>
       <c r="G66" s="3">
-        <v>97300</v>
+        <v>93400</v>
       </c>
       <c r="H66" s="3">
-        <v>114400</v>
+        <v>96700</v>
       </c>
       <c r="I66" s="3">
-        <v>112600</v>
+        <v>113700</v>
       </c>
       <c r="J66" s="3">
+        <v>111900</v>
+      </c>
+      <c r="K66" s="3">
         <v>119100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>122100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>99900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>96800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>91300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>84500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>89200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>83600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>79300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5068,11 +5235,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>218000</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,71 +5332,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-43600</v>
+        <v>-40900</v>
       </c>
       <c r="E72" s="3">
-        <v>-46200</v>
+        <v>-43400</v>
       </c>
       <c r="F72" s="3">
-        <v>-45800</v>
+        <v>-45900</v>
       </c>
       <c r="G72" s="3">
-        <v>-44200</v>
+        <v>-45500</v>
       </c>
       <c r="H72" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="J72" s="3">
         <v>-48500</v>
       </c>
-      <c r="I72" s="3">
-        <v>-48800</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-44300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-34800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-32800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-41500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-33900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-41600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-41700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-45000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-38300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-49100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-53500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-57700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,71 +5652,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>337300</v>
+        <v>337700</v>
       </c>
       <c r="E76" s="3">
-        <v>337200</v>
+        <v>335200</v>
       </c>
       <c r="F76" s="3">
-        <v>336200</v>
+        <v>335100</v>
       </c>
       <c r="G76" s="3">
-        <v>347300</v>
+        <v>334100</v>
       </c>
       <c r="H76" s="3">
-        <v>346700</v>
+        <v>345100</v>
       </c>
       <c r="I76" s="3">
-        <v>337300</v>
+        <v>344600</v>
       </c>
       <c r="J76" s="3">
+        <v>335200</v>
+      </c>
+      <c r="K76" s="3">
         <v>332800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>337800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>347100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>342300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>371300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>361400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>386700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>395500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>418900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>406900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>398100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>379300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-54600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,8 +6487,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6351,8 +6567,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6457,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6688,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,8 +7267,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7102,8 +7347,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,8 +7427,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7254,6 +7505,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>SY</t>
   </si>
@@ -656,365 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>54000</v>
+        <v>57400</v>
       </c>
       <c r="E8" s="3">
-        <v>53200</v>
+        <v>44900</v>
       </c>
       <c r="F8" s="3">
-        <v>56900</v>
+        <v>55100</v>
       </c>
       <c r="G8" s="3">
-        <v>42800</v>
+        <v>54300</v>
       </c>
       <c r="H8" s="3">
-        <v>44900</v>
+        <v>58100</v>
       </c>
       <c r="I8" s="3">
+        <v>43700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>45800</v>
+      </c>
+      <c r="K8" s="3">
         <v>44700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>42700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>41700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>62100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>61300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>64200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>51600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>59100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>53000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>48400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>28800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>55200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>46600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>43500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>31400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>26600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>23600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>21800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>16300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19000</v>
+        <v>21900</v>
       </c>
       <c r="E9" s="3">
-        <v>19700</v>
+        <v>16500</v>
       </c>
       <c r="F9" s="3">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="G9" s="3">
-        <v>15700</v>
+        <v>20100</v>
       </c>
       <c r="H9" s="3">
-        <v>12200</v>
+        <v>21200</v>
       </c>
       <c r="I9" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K9" s="3">
         <v>13000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>14400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>14800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>17500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>8400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>7500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>8900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>7500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>6800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>9000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>8300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>7600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>5500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>3000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>34900</v>
+        <v>35600</v>
       </c>
       <c r="E10" s="3">
-        <v>33500</v>
+        <v>28300</v>
       </c>
       <c r="F10" s="3">
-        <v>36200</v>
+        <v>35700</v>
       </c>
       <c r="G10" s="3">
-        <v>27100</v>
+        <v>34200</v>
       </c>
       <c r="H10" s="3">
-        <v>32700</v>
+        <v>36900</v>
       </c>
       <c r="I10" s="3">
+        <v>27700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>33400</v>
+      </c>
+      <c r="K10" s="3">
         <v>31700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>28300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>26900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>44500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>48600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>55900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>44100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>50200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>44900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>40900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>22000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>46100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>38300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>35900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>25800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>22000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>20200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>18800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>14200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1069,96 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>6200</v>
+        <v>6000</v>
       </c>
       <c r="E12" s="3">
-        <v>7000</v>
+        <v>5600</v>
       </c>
       <c r="F12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="G12" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>8700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>9300</v>
       </c>
       <c r="M12" s="3">
         <v>11000</v>
       </c>
       <c r="N12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="P12" s="3">
         <v>10300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>10000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>9900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>9300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>7700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>6800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>8400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>6100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7900</v>
-      </c>
-      <c r="W12" s="3">
-        <v>4800</v>
-      </c>
-      <c r="X12" s="3">
-        <v>3800</v>
       </c>
       <c r="Y12" s="3">
         <v>4800</v>
       </c>
       <c r="Z12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AB12" s="3">
         <v>3000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,68 +1237,74 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1274,17 +1314,23 @@
       <c r="Y14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1363,8 +1409,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1442,182 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>54700</v>
+        <v>56500</v>
       </c>
       <c r="E17" s="3">
-        <v>53500</v>
+        <v>50100</v>
       </c>
       <c r="F17" s="3">
-        <v>59800</v>
+        <v>55800</v>
       </c>
       <c r="G17" s="3">
-        <v>47500</v>
+        <v>54600</v>
       </c>
       <c r="H17" s="3">
-        <v>41600</v>
+        <v>61000</v>
       </c>
       <c r="I17" s="3">
+        <v>48400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>42400</v>
+      </c>
+      <c r="K17" s="3">
         <v>46800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>48500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>52600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>68900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>61100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>56000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>60300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>55000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>57400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>49800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>36100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>43900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>43500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>41900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>25600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>21700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>26700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>20700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>12100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J18" s="3">
         <v>3400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>8200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-8600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-7300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>11200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>4900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>4300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,88 +1646,96 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>800</v>
       </c>
       <c r="M20" s="3">
         <v>1200</v>
       </c>
       <c r="N20" s="3">
+        <v>800</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>4500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1740,8 +1814,14 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1820,168 +1900,186 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
-        <v>2300</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J23" s="3">
         <v>4100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-9600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-6000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>9600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>15200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>5300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>8100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>6000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>4700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-2300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2158,186 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F26" s="3">
         <v>2700</v>
       </c>
-      <c r="E26" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K26" s="3">
+        <v>300</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="O26" s="3">
+        <v>800</v>
+      </c>
+      <c r="P26" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="R26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3">
+        <v>300</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="V26" s="3">
+        <v>10800</v>
+      </c>
+      <c r="W26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="X26" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC26" s="3">
         <v>4400</v>
       </c>
-      <c r="I26" s="3">
-        <v>300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>8000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="P26" s="3">
-        <v>5300</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="T26" s="3">
-        <v>10800</v>
-      </c>
-      <c r="U26" s="3">
-        <v>4900</v>
-      </c>
-      <c r="V26" s="3">
-        <v>4500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>7000</v>
-      </c>
-      <c r="X26" s="3">
-        <v>5900</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>4400</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-9300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-6500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>10800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>4900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2416,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2502,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2588,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2674,186 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-800</v>
       </c>
       <c r="M32" s="3">
         <v>-1200</v>
       </c>
       <c r="N32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-4500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-9300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>8200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-6500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>10800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>4900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2932,191 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-9300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>8200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-6500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>10800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>4900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3145,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,77 +3177,79 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>58900</v>
+        <v>64400</v>
       </c>
       <c r="E41" s="3">
-        <v>60600</v>
+        <v>63200</v>
       </c>
       <c r="F41" s="3">
-        <v>104800</v>
+        <v>60100</v>
       </c>
       <c r="G41" s="3">
-        <v>112700</v>
+        <v>61800</v>
       </c>
       <c r="H41" s="3">
-        <v>95900</v>
+        <v>107000</v>
       </c>
       <c r="I41" s="3">
+        <v>115000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>97900</v>
+      </c>
+      <c r="K41" s="3">
         <v>98600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>203300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>217500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>183900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>224100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>163300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>139800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>156900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>81400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>232000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>144600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>136200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>94000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>169200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>108000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3085,77 +3259,83 @@
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>124500</v>
+        <v>99400</v>
       </c>
       <c r="E42" s="3">
-        <v>131400</v>
+        <v>123300</v>
       </c>
       <c r="F42" s="3">
-        <v>105300</v>
+        <v>127000</v>
       </c>
       <c r="G42" s="3">
-        <v>89500</v>
+        <v>134100</v>
       </c>
       <c r="H42" s="3">
-        <v>121000</v>
+        <v>107500</v>
       </c>
       <c r="I42" s="3">
+        <v>91400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>123500</v>
+      </c>
+      <c r="K42" s="3">
         <v>125500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>15300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>15400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>56500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>33300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>154200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>230000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>212600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>329000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>190600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>288200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>299200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>331800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>238000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>85300</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3165,77 +3345,83 @@
       <c r="AB42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>16300</v>
+      </c>
+      <c r="H43" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K43" s="3">
         <v>12400</v>
       </c>
-      <c r="E43" s="3">
-        <v>16000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>11000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>11600</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
+        <v>11700</v>
+      </c>
+      <c r="M43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="N43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="O43" s="3">
+        <v>15500</v>
+      </c>
+      <c r="P43" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Q43" s="3">
         <v>12400</v>
       </c>
-      <c r="J43" s="3">
-        <v>11700</v>
-      </c>
-      <c r="K43" s="3">
-        <v>12200</v>
-      </c>
-      <c r="L43" s="3">
-        <v>12100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>15500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>14000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>12400</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>10700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>10300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>9800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>8200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>7000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3245,47 +3431,53 @@
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>16400</v>
+        <v>20200</v>
       </c>
       <c r="E44" s="3">
-        <v>15900</v>
+        <v>17800</v>
       </c>
       <c r="F44" s="3">
+        <v>16800</v>
+      </c>
+      <c r="G44" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H44" s="3">
+        <v>17300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>16800</v>
+      </c>
+      <c r="J44" s="3">
         <v>17000</v>
       </c>
-      <c r="G44" s="3">
-        <v>16500</v>
-      </c>
-      <c r="H44" s="3">
-        <v>16600</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>14500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>13100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>12400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>12700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>13000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3298,11 +3490,11 @@
       <c r="S44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3325,77 +3517,83 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>25800</v>
+        <v>45200</v>
       </c>
       <c r="E45" s="3">
-        <v>27400</v>
+        <v>28200</v>
       </c>
       <c r="F45" s="3">
-        <v>23200</v>
+        <v>26300</v>
       </c>
       <c r="G45" s="3">
-        <v>19900</v>
+        <v>27900</v>
       </c>
       <c r="H45" s="3">
-        <v>19600</v>
+        <v>23700</v>
       </c>
       <c r="I45" s="3">
+        <v>20300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K45" s="3">
         <v>22900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>19800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>14100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>14800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>17100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>17500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>12600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>9100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>11300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>9600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>13000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>13000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>13500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>11900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>8700</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3405,77 +3603,83 @@
       <c r="AB45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>237900</v>
+        <v>245100</v>
       </c>
       <c r="E46" s="3">
-        <v>251200</v>
+        <v>246500</v>
       </c>
       <c r="F46" s="3">
-        <v>263500</v>
+        <v>242800</v>
       </c>
       <c r="G46" s="3">
-        <v>249600</v>
+        <v>256300</v>
       </c>
       <c r="H46" s="3">
-        <v>264800</v>
+        <v>268900</v>
       </c>
       <c r="I46" s="3">
+        <v>254700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>270200</v>
+      </c>
+      <c r="K46" s="3">
         <v>274000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>263300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>271600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>279900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>302900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>348900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>394800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>389200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>431900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>441900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>453900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>455300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>446200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>423400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>206300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3485,77 +3689,83 @@
       <c r="AB46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E47" s="3">
         <v>36100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
+        <v>36800</v>
+      </c>
+      <c r="G47" s="3">
+        <v>35600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>35500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>34400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>32100</v>
+      </c>
+      <c r="K47" s="3">
+        <v>32300</v>
+      </c>
+      <c r="L47" s="3">
+        <v>34700</v>
+      </c>
+      <c r="M47" s="3">
         <v>34900</v>
       </c>
-      <c r="F47" s="3">
-        <v>34800</v>
-      </c>
-      <c r="G47" s="3">
-        <v>33700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>31500</v>
-      </c>
-      <c r="I47" s="3">
-        <v>32300</v>
-      </c>
-      <c r="J47" s="3">
-        <v>34700</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>34900</v>
       </c>
-      <c r="L47" s="3">
-        <v>34900</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>36000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>31800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>25000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>23100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>6100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>6300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>7000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>7100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>4900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>2300</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3565,77 +3775,83 @@
       <c r="AB47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>32500</v>
+        <v>39100</v>
       </c>
       <c r="E48" s="3">
-        <v>20600</v>
+        <v>33200</v>
       </c>
       <c r="F48" s="3">
-        <v>22600</v>
+        <v>33200</v>
       </c>
       <c r="G48" s="3">
-        <v>23300</v>
+        <v>21000</v>
       </c>
       <c r="H48" s="3">
-        <v>24700</v>
+        <v>23000</v>
       </c>
       <c r="I48" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>25200</v>
+      </c>
+      <c r="K48" s="3">
         <v>25800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>28100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>29400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>30400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>32400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>18600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>20200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>20900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>23600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>24600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>27400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>27200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>28800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>29700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>26600</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3645,65 +3861,71 @@
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>94800</v>
+        <v>95000</v>
       </c>
       <c r="E49" s="3">
-        <v>95600</v>
+        <v>95800</v>
       </c>
       <c r="F49" s="3">
-        <v>96400</v>
+        <v>96700</v>
       </c>
       <c r="G49" s="3">
-        <v>97200</v>
+        <v>97500</v>
       </c>
       <c r="H49" s="3">
-        <v>98100</v>
+        <v>98300</v>
       </c>
       <c r="I49" s="3">
+        <v>99200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>100100</v>
+      </c>
+      <c r="K49" s="3">
         <v>99000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>99800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>101300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>101400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>107500</v>
-      </c>
-      <c r="N49" s="3">
-        <v>15100</v>
-      </c>
-      <c r="O49" s="3">
-        <v>15300</v>
       </c>
       <c r="P49" s="3">
         <v>15100</v>
       </c>
       <c r="Q49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="R49" s="3">
+        <v>15100</v>
+      </c>
+      <c r="S49" s="3">
         <v>6100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>6200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>6900</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3716,17 +3938,23 @@
       <c r="Y49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +4033,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,77 +4119,83 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>42900</v>
+        <v>37200</v>
       </c>
       <c r="E52" s="3">
-        <v>30500</v>
+        <v>37900</v>
       </c>
       <c r="F52" s="3">
-        <v>19900</v>
+        <v>43800</v>
       </c>
       <c r="G52" s="3">
-        <v>23600</v>
+        <v>31200</v>
       </c>
       <c r="H52" s="3">
-        <v>22700</v>
+        <v>20300</v>
       </c>
       <c r="I52" s="3">
+        <v>24100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>23100</v>
+      </c>
+      <c r="K52" s="3">
         <v>27200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>21200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>13200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>32400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>28100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>15900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>9900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>9800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>7700</v>
-      </c>
-      <c r="S52" s="3">
-        <v>8200</v>
       </c>
       <c r="T52" s="3">
         <v>7700</v>
       </c>
       <c r="U52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="V52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="W52" s="3">
         <v>6600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>7500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3965,8 +4205,14 @@
       <c r="AB52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,77 +4291,83 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>444100</v>
+        <v>455700</v>
       </c>
       <c r="E54" s="3">
-        <v>432800</v>
+        <v>449500</v>
       </c>
       <c r="F54" s="3">
-        <v>437100</v>
+        <v>453200</v>
       </c>
       <c r="G54" s="3">
-        <v>427500</v>
+        <v>441600</v>
       </c>
       <c r="H54" s="3">
-        <v>441800</v>
+        <v>446100</v>
       </c>
       <c r="I54" s="3">
+        <v>436200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>450800</v>
+      </c>
+      <c r="K54" s="3">
         <v>458300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>447100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>451800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>459900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>511200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>442400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>471200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>458200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>477500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>486800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>503400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>497300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>487300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>462900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>242700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4125,8 +4377,14 @@
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4413,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,52 +4445,54 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
       <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>300</v>
       </c>
       <c r="Q57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
@@ -4239,22 +4501,22 @@
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>300</v>
+      </c>
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>16</v>
+      <c r="Y57" s="3">
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>16</v>
@@ -4265,19 +4527,25 @@
       <c r="AB57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4100</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>16</v>
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4200</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>16</v>
@@ -4291,11 +4559,11 @@
       <c r="J58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4345,77 +4613,83 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70500</v>
+        <v>71800</v>
       </c>
       <c r="E59" s="3">
-        <v>77100</v>
+        <v>72400</v>
       </c>
       <c r="F59" s="3">
-        <v>81300</v>
+        <v>71900</v>
       </c>
       <c r="G59" s="3">
-        <v>71500</v>
+        <v>78600</v>
       </c>
       <c r="H59" s="3">
-        <v>73500</v>
+        <v>83000</v>
       </c>
       <c r="I59" s="3">
+        <v>73000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>75000</v>
+      </c>
+      <c r="K59" s="3">
         <v>94900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>91400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>96800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>98300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>135800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>84400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>82800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>79100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>74000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>73200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>64100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>71400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>68700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>61900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>57400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4425,77 +4699,83 @@
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>74700</v>
+        <v>77500</v>
       </c>
       <c r="E60" s="3">
-        <v>77200</v>
+        <v>76700</v>
       </c>
       <c r="F60" s="3">
-        <v>81400</v>
+        <v>76200</v>
       </c>
       <c r="G60" s="3">
-        <v>71600</v>
+        <v>78700</v>
       </c>
       <c r="H60" s="3">
-        <v>74300</v>
+        <v>83000</v>
       </c>
       <c r="I60" s="3">
+        <v>73000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>75900</v>
+      </c>
+      <c r="K60" s="3">
         <v>94900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>91400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>96800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>98400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>135900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>84700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>83100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>79500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>74400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>73600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>64500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>71800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>69200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>62600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>57400</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4505,8 +4785,14 @@
       <c r="AB60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4585,77 +4871,83 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15600</v>
+        <v>19400</v>
       </c>
       <c r="E62" s="3">
-        <v>4500</v>
+        <v>17000</v>
       </c>
       <c r="F62" s="3">
-        <v>4900</v>
+        <v>15900</v>
       </c>
       <c r="G62" s="3">
-        <v>5600</v>
+        <v>4600</v>
       </c>
       <c r="H62" s="3">
-        <v>7200</v>
+        <v>5000</v>
       </c>
       <c r="I62" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K62" s="3">
         <v>9100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>10800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>12400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>13900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>14600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>12500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>13700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>14100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>16300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>17800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>20000</v>
-      </c>
-      <c r="T62" s="3">
-        <v>18600</v>
       </c>
       <c r="U62" s="3">
         <v>20000</v>
       </c>
       <c r="V62" s="3">
+        <v>18600</v>
+      </c>
+      <c r="W62" s="3">
+        <v>20000</v>
+      </c>
+      <c r="X62" s="3">
         <v>21000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>21900</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4665,8 +4957,14 @@
       <c r="AB62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +5043,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +5129,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,77 +5215,83 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>106400</v>
+        <v>113700</v>
       </c>
       <c r="E66" s="3">
-        <v>97600</v>
+        <v>110400</v>
       </c>
       <c r="F66" s="3">
-        <v>102100</v>
+        <v>108600</v>
       </c>
       <c r="G66" s="3">
-        <v>93400</v>
+        <v>99600</v>
       </c>
       <c r="H66" s="3">
-        <v>96700</v>
+        <v>104200</v>
       </c>
       <c r="I66" s="3">
+        <v>95300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>98700</v>
+      </c>
+      <c r="K66" s="3">
         <v>113700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>111900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>119100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>122100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>164200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>100200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>99900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>96800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>90700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>91300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>84500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>90400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>89200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>83600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>79300</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4985,8 +5301,14 @@
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5337,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5419,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5505,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5238,14 +5574,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>218000</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5591,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,77 +5677,83 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-40900</v>
+        <v>-42100</v>
       </c>
       <c r="E72" s="3">
-        <v>-43400</v>
+        <v>-44800</v>
       </c>
       <c r="F72" s="3">
-        <v>-45900</v>
+        <v>-41800</v>
       </c>
       <c r="G72" s="3">
-        <v>-45500</v>
+        <v>-44200</v>
       </c>
       <c r="H72" s="3">
-        <v>-43900</v>
+        <v>-46800</v>
       </c>
       <c r="I72" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-48200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-48500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-44300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-34800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-31900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-32800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-41500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-41600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-41700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-45000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-38300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-49100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-53500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-57700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5415,8 +5763,14 @@
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5849,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5935,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,77 +6021,83 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>337700</v>
+        <v>342000</v>
       </c>
       <c r="E76" s="3">
+        <v>339200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>344600</v>
+      </c>
+      <c r="G76" s="3">
+        <v>342000</v>
+      </c>
+      <c r="H76" s="3">
+        <v>341900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>340900</v>
+      </c>
+      <c r="J76" s="3">
+        <v>352200</v>
+      </c>
+      <c r="K76" s="3">
+        <v>344600</v>
+      </c>
+      <c r="L76" s="3">
         <v>335200</v>
       </c>
-      <c r="F76" s="3">
-        <v>335100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>334100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>345100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>344600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>335200</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>332800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>337800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>347100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>342300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>371300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>361400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>386700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>395500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>418900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>406900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>398100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>379300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-54600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5735,8 +6107,14 @@
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6193,191 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-9300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>8200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-6500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>10800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>4900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6406,10 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6090,8 +6488,14 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6574,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6660,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6746,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6832,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,8 +6918,14 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6570,8 +7004,14 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +7040,10 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6680,8 +7122,14 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +7208,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7294,14 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6920,8 +7380,14 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7416,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7498,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7584,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7670,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7756,14 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7350,8 +7842,14 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,8 +7928,14 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7508,6 +8012,12 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>SY</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>57400</v>
+        <v>53000</v>
       </c>
       <c r="E8" s="3">
-        <v>44900</v>
+        <v>56100</v>
       </c>
       <c r="F8" s="3">
+        <v>44100</v>
+      </c>
+      <c r="G8" s="3">
         <v>55100</v>
       </c>
-      <c r="G8" s="3">
-        <v>54300</v>
-      </c>
       <c r="H8" s="3">
-        <v>58100</v>
+        <v>52800</v>
       </c>
       <c r="I8" s="3">
-        <v>43700</v>
+        <v>56800</v>
       </c>
       <c r="J8" s="3">
+        <v>45100</v>
+      </c>
+      <c r="K8" s="3">
         <v>45800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>44700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>62100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>61300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>64200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>51600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>59100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>53000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>48400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>55200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>46600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>43500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>21800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>21900</v>
+        <v>20300</v>
       </c>
       <c r="E9" s="3">
-        <v>16500</v>
+        <v>21300</v>
       </c>
       <c r="F9" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G9" s="3">
         <v>19400</v>
       </c>
-      <c r="G9" s="3">
-        <v>20100</v>
-      </c>
       <c r="H9" s="3">
-        <v>21200</v>
+        <v>19500</v>
       </c>
       <c r="I9" s="3">
-        <v>16000</v>
+        <v>20700</v>
       </c>
       <c r="J9" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K9" s="3">
         <v>12400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>35600</v>
+        <v>32700</v>
       </c>
       <c r="E10" s="3">
+        <v>34700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>27800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>35700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>33300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>36100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>28600</v>
+      </c>
+      <c r="K10" s="3">
+        <v>33400</v>
+      </c>
+      <c r="L10" s="3">
+        <v>31700</v>
+      </c>
+      <c r="M10" s="3">
         <v>28300</v>
       </c>
-      <c r="F10" s="3">
-        <v>35700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>34200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>36900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>27700</v>
-      </c>
-      <c r="J10" s="3">
-        <v>33400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>31700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>28300</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>44500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>48600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>44100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>50200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>44900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>46100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>38300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>35900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>14200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1084,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>6000</v>
+        <v>5700</v>
       </c>
       <c r="E12" s="3">
-        <v>5600</v>
+        <v>5800</v>
       </c>
       <c r="F12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G12" s="3">
         <v>6300</v>
       </c>
-      <c r="G12" s="3">
-        <v>7100</v>
-      </c>
       <c r="H12" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="I12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="N12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>10300</v>
+      </c>
+      <c r="R12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="S12" s="3">
+        <v>9900</v>
+      </c>
+      <c r="T12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="U12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="V12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="W12" s="3">
+        <v>8400</v>
+      </c>
+      <c r="X12" s="3">
+        <v>6100</v>
+      </c>
+      <c r="Y12" s="3">
         <v>7900</v>
       </c>
-      <c r="J12" s="3">
-        <v>5800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>8700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>9300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>10300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>10000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>9900</v>
-      </c>
-      <c r="S12" s="3">
-        <v>9300</v>
-      </c>
-      <c r="T12" s="3">
-        <v>7700</v>
-      </c>
-      <c r="U12" s="3">
-        <v>6800</v>
-      </c>
-      <c r="V12" s="3">
-        <v>8400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>6100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>7900</v>
-      </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,71 +1260,74 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3">
         <v>9100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1320,8 +1340,8 @@
       <c r="AA14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1329,31 +1349,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>56500</v>
+        <v>52300</v>
       </c>
       <c r="E17" s="3">
-        <v>50100</v>
+        <v>55100</v>
       </c>
       <c r="F17" s="3">
+        <v>49200</v>
+      </c>
+      <c r="G17" s="3">
         <v>55800</v>
       </c>
-      <c r="G17" s="3">
-        <v>54600</v>
-      </c>
       <c r="H17" s="3">
-        <v>61000</v>
+        <v>53100</v>
       </c>
       <c r="I17" s="3">
-        <v>48400</v>
+        <v>59700</v>
       </c>
       <c r="J17" s="3">
+        <v>50000</v>
+      </c>
+      <c r="K17" s="3">
         <v>42400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>68900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>61100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>60300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>49800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>36100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>41900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>25600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E18" s="3">
-        <v>-5200</v>
+        <v>900</v>
       </c>
       <c r="F18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
-        <v>-4700</v>
-      </c>
       <c r="J18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K18" s="3">
         <v>3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,117 +1681,121 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>1500</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>2700</v>
+        <v>-300</v>
       </c>
       <c r="H20" s="3">
-        <v>2600</v>
+        <v>-800</v>
       </c>
       <c r="I20" s="3">
-        <v>2500</v>
+        <v>-200</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1400</v>
       </c>
       <c r="Q20" s="3">
         <v>1400</v>
       </c>
       <c r="R20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S20" s="3">
         <v>2900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>2200</v>
       </c>
       <c r="T20" s="3">
         <v>2200</v>
       </c>
       <c r="U20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-3300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -1820,31 +1857,34 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1906,180 +1946,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E23" s="3">
-        <v>-3200</v>
+        <v>2400</v>
       </c>
       <c r="F23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
-        <v>2400</v>
-      </c>
       <c r="H23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>15200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>-400</v>
       </c>
       <c r="F24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>2700</v>
       </c>
       <c r="G26" s="3">
         <v>2700</v>
       </c>
       <c r="H26" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="E27" s="3">
-        <v>-3000</v>
+        <v>2600</v>
       </c>
       <c r="F27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G27" s="3">
         <v>2500</v>
       </c>
-      <c r="G27" s="3">
-        <v>2600</v>
-      </c>
       <c r="H27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1500</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
-        <v>-2000</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-2700</v>
+        <v>300</v>
       </c>
       <c r="H32" s="3">
-        <v>-2600</v>
+        <v>800</v>
       </c>
       <c r="I32" s="3">
-        <v>-2500</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1400</v>
       </c>
       <c r="Q32" s="3">
         <v>-1400</v>
       </c>
       <c r="R32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S32" s="3">
         <v>-2900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-2200</v>
       </c>
       <c r="T32" s="3">
         <v>-2200</v>
       </c>
       <c r="U32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="E33" s="3">
-        <v>-3000</v>
+        <v>2600</v>
       </c>
       <c r="F33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G33" s="3">
         <v>2500</v>
       </c>
-      <c r="G33" s="3">
-        <v>2600</v>
-      </c>
       <c r="H33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="E35" s="3">
-        <v>-3000</v>
+        <v>2600</v>
       </c>
       <c r="F35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G35" s="3">
         <v>2500</v>
       </c>
-      <c r="G35" s="3">
-        <v>2600</v>
-      </c>
       <c r="H35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,80 +3265,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>64400</v>
+        <v>66600</v>
       </c>
       <c r="E41" s="3">
-        <v>63200</v>
+        <v>62900</v>
       </c>
       <c r="F41" s="3">
+        <v>62100</v>
+      </c>
+      <c r="G41" s="3">
         <v>60100</v>
       </c>
-      <c r="G41" s="3">
-        <v>61800</v>
-      </c>
       <c r="H41" s="3">
-        <v>107000</v>
+        <v>60100</v>
       </c>
       <c r="I41" s="3">
-        <v>115000</v>
+        <v>104600</v>
       </c>
       <c r="J41" s="3">
+        <v>118800</v>
+      </c>
+      <c r="K41" s="3">
         <v>97900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>98600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>203300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>217500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>183900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>163300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>139800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>156900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>81400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>232000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>144600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>136200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>94000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>169200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>108000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3265,80 +3352,83 @@
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>99400</v>
+        <v>97100</v>
       </c>
       <c r="E42" s="3">
-        <v>123300</v>
+        <v>97000</v>
       </c>
       <c r="F42" s="3">
+        <v>121200</v>
+      </c>
+      <c r="G42" s="3">
         <v>127000</v>
       </c>
-      <c r="G42" s="3">
-        <v>134100</v>
-      </c>
       <c r="H42" s="3">
-        <v>107500</v>
+        <v>130300</v>
       </c>
       <c r="I42" s="3">
-        <v>91400</v>
+        <v>105100</v>
       </c>
       <c r="J42" s="3">
+        <v>94300</v>
+      </c>
+      <c r="K42" s="3">
         <v>123500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>125500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>56500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>33300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>154200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>230000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>212600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>329000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>190600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>288200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>299200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>331800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>238000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>85300</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3351,80 +3441,83 @@
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>15900</v>
+        <v>21300</v>
       </c>
       <c r="E43" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>13800</v>
+      </c>
+      <c r="G43" s="3">
+        <v>28300</v>
+      </c>
+      <c r="H43" s="3">
+        <v>15800</v>
+      </c>
+      <c r="I43" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K43" s="3">
+        <v>11900</v>
+      </c>
+      <c r="L43" s="3">
+        <v>12400</v>
+      </c>
+      <c r="M43" s="3">
+        <v>11700</v>
+      </c>
+      <c r="N43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="O43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>15500</v>
+      </c>
+      <c r="Q43" s="3">
         <v>14000</v>
       </c>
-      <c r="F43" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>16300</v>
-      </c>
-      <c r="H43" s="3">
-        <v>13400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>11200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>11900</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="R43" s="3">
         <v>12400</v>
       </c>
-      <c r="L43" s="3">
-        <v>11700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>12200</v>
-      </c>
-      <c r="N43" s="3">
-        <v>12100</v>
-      </c>
-      <c r="O43" s="3">
-        <v>15500</v>
-      </c>
-      <c r="P43" s="3">
-        <v>14000</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>12400</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8200</v>
-      </c>
-      <c r="V43" s="3">
-        <v>7000</v>
       </c>
       <c r="W43" s="3">
         <v>7000</v>
       </c>
       <c r="X43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y43" s="3">
         <v>4300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3437,50 +3530,53 @@
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>20200</v>
+        <v>20800</v>
       </c>
       <c r="E44" s="3">
-        <v>17800</v>
+        <v>19700</v>
       </c>
       <c r="F44" s="3">
+        <v>17500</v>
+      </c>
+      <c r="G44" s="3">
         <v>16800</v>
       </c>
-      <c r="G44" s="3">
-        <v>16200</v>
-      </c>
       <c r="H44" s="3">
-        <v>17300</v>
+        <v>15800</v>
       </c>
       <c r="I44" s="3">
-        <v>16800</v>
+        <v>17000</v>
       </c>
       <c r="J44" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K44" s="3">
         <v>17000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13000</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3496,8 +3592,8 @@
       <c r="U44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3523,80 +3619,83 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45200</v>
+        <v>31500</v>
       </c>
       <c r="E45" s="3">
-        <v>28200</v>
+        <v>32700</v>
       </c>
       <c r="F45" s="3">
-        <v>26300</v>
+        <v>24600</v>
       </c>
       <c r="G45" s="3">
-        <v>27900</v>
+        <v>1700</v>
       </c>
       <c r="H45" s="3">
-        <v>23700</v>
+        <v>25000</v>
       </c>
       <c r="I45" s="3">
-        <v>20300</v>
+        <v>21000</v>
       </c>
       <c r="J45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="K45" s="3">
         <v>20000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9600</v>
-      </c>
-      <c r="U45" s="3">
-        <v>13000</v>
       </c>
       <c r="V45" s="3">
         <v>13000</v>
       </c>
       <c r="W45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="X45" s="3">
         <v>13500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8700</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3609,80 +3708,83 @@
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>245100</v>
+        <v>252100</v>
       </c>
       <c r="E46" s="3">
-        <v>246500</v>
+        <v>239200</v>
       </c>
       <c r="F46" s="3">
+        <v>242200</v>
+      </c>
+      <c r="G46" s="3">
         <v>242800</v>
       </c>
-      <c r="G46" s="3">
-        <v>256300</v>
-      </c>
       <c r="H46" s="3">
-        <v>268900</v>
+        <v>249200</v>
       </c>
       <c r="I46" s="3">
-        <v>254700</v>
+        <v>263000</v>
       </c>
       <c r="J46" s="3">
+        <v>263100</v>
+      </c>
+      <c r="K46" s="3">
         <v>270200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>274000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>263300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>271600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>279900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>302900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>348900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>394800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>389200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>431900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>441900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>453900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>455300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>446200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>423400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>206300</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3695,80 +3797,83 @@
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>39300</v>
+        <v>41000</v>
       </c>
       <c r="E47" s="3">
-        <v>36100</v>
+        <v>38300</v>
       </c>
       <c r="F47" s="3">
+        <v>35500</v>
+      </c>
+      <c r="G47" s="3">
         <v>36800</v>
       </c>
-      <c r="G47" s="3">
-        <v>35600</v>
-      </c>
       <c r="H47" s="3">
+        <v>34600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>34700</v>
+      </c>
+      <c r="J47" s="3">
         <v>35500</v>
       </c>
-      <c r="I47" s="3">
-        <v>34400</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>32100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34700</v>
-      </c>
-      <c r="M47" s="3">
-        <v>34900</v>
       </c>
       <c r="N47" s="3">
         <v>34900</v>
       </c>
       <c r="O47" s="3">
+        <v>34900</v>
+      </c>
+      <c r="P47" s="3">
         <v>36000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>25000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>23100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2300</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3781,80 +3886,83 @@
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>39100</v>
+        <v>44700</v>
       </c>
       <c r="E48" s="3">
+        <v>38100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>32600</v>
+      </c>
+      <c r="G48" s="3">
         <v>33200</v>
       </c>
-      <c r="F48" s="3">
-        <v>33200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>21000</v>
-      </c>
       <c r="H48" s="3">
-        <v>23000</v>
+        <v>20400</v>
       </c>
       <c r="I48" s="3">
-        <v>23800</v>
+        <v>22500</v>
       </c>
       <c r="J48" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K48" s="3">
         <v>25200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>29700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26600</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3867,68 +3975,71 @@
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>95000</v>
+        <v>95800</v>
       </c>
       <c r="E49" s="3">
-        <v>95800</v>
+        <v>92700</v>
       </c>
       <c r="F49" s="3">
+        <v>94200</v>
+      </c>
+      <c r="G49" s="3">
         <v>96700</v>
       </c>
-      <c r="G49" s="3">
-        <v>97500</v>
-      </c>
       <c r="H49" s="3">
-        <v>98300</v>
+        <v>94800</v>
       </c>
       <c r="I49" s="3">
-        <v>99200</v>
+        <v>96200</v>
       </c>
       <c r="J49" s="3">
+        <v>102500</v>
+      </c>
+      <c r="K49" s="3">
         <v>100100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>99000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>99800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>101300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>101400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>107500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3944,8 +4055,8 @@
       <c r="AA49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,80 +4242,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>37200</v>
+        <v>25800</v>
       </c>
       <c r="E52" s="3">
-        <v>37900</v>
+        <v>25300</v>
       </c>
       <c r="F52" s="3">
-        <v>43800</v>
+        <v>26200</v>
       </c>
       <c r="G52" s="3">
-        <v>31200</v>
+        <v>32800</v>
       </c>
       <c r="H52" s="3">
-        <v>20300</v>
+        <v>21100</v>
       </c>
       <c r="I52" s="3">
-        <v>24100</v>
+        <v>11000</v>
       </c>
       <c r="J52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K52" s="3">
         <v>23100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7500</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,80 +4420,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>455700</v>
+        <v>471000</v>
       </c>
       <c r="E54" s="3">
-        <v>449500</v>
+        <v>444800</v>
       </c>
       <c r="F54" s="3">
-        <v>453200</v>
+        <v>441600</v>
       </c>
       <c r="G54" s="3">
-        <v>441600</v>
+        <v>453300</v>
       </c>
       <c r="H54" s="3">
-        <v>446100</v>
+        <v>429300</v>
       </c>
       <c r="I54" s="3">
-        <v>436200</v>
+        <v>436300</v>
       </c>
       <c r="J54" s="3">
+        <v>450500</v>
+      </c>
+      <c r="K54" s="3">
         <v>450800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>458300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>447100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>451800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>459900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>511200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>442400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>471200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>458200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>477500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>486800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>503400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>497300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>487300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>462900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>242700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,35 +4577,36 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -4483,13 +4614,13 @@
         <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
@@ -4498,28 +4629,28 @@
         <v>300</v>
       </c>
       <c r="S57" s="3">
+        <v>300</v>
+      </c>
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="U57" s="3">
-        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>400</v>
       </c>
       <c r="W57" s="3">
+        <v>400</v>
+      </c>
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>16</v>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>16</v>
@@ -4533,31 +4664,34 @@
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5600</v>
+        <v>18500</v>
       </c>
       <c r="E58" s="3">
-        <v>4200</v>
+        <v>9200</v>
       </c>
       <c r="F58" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>16</v>
+        <v>7800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>7400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>16</v>
@@ -4565,8 +4699,8 @@
       <c r="L58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4619,80 +4753,83 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>71800</v>
+        <v>21200</v>
       </c>
       <c r="E59" s="3">
-        <v>72400</v>
+        <v>13200</v>
       </c>
       <c r="F59" s="3">
-        <v>71900</v>
+        <v>27400</v>
       </c>
       <c r="G59" s="3">
-        <v>78600</v>
+        <v>40700</v>
       </c>
       <c r="H59" s="3">
-        <v>83000</v>
+        <v>24200</v>
       </c>
       <c r="I59" s="3">
-        <v>73000</v>
+        <v>23100</v>
       </c>
       <c r="J59" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K59" s="3">
         <v>75000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>94900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>96800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>98300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>135800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>82800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>79100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>73200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>64100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>71400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>68700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>61900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>57400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4705,80 +4842,83 @@
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>77500</v>
+        <v>86700</v>
       </c>
       <c r="E60" s="3">
-        <v>76700</v>
+        <v>75600</v>
       </c>
       <c r="F60" s="3">
+        <v>75300</v>
+      </c>
+      <c r="G60" s="3">
         <v>76200</v>
       </c>
-      <c r="G60" s="3">
-        <v>78700</v>
-      </c>
       <c r="H60" s="3">
-        <v>83000</v>
+        <v>76500</v>
       </c>
       <c r="I60" s="3">
-        <v>73000</v>
+        <v>81200</v>
       </c>
       <c r="J60" s="3">
+        <v>75400</v>
+      </c>
+      <c r="K60" s="3">
         <v>75900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>94900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>91400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>96800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>98400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>135900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>84700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>83100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>79500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>74400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>73600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>64500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>71800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>69200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>62600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>57400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4791,31 +4931,34 @@
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>17800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4877,80 +5020,83 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19400</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>17000</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>15900</v>
+        <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>4600</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>5700</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>300</v>
+      </c>
+      <c r="K62" s="3">
         <v>7300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,80 +5376,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>94500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>92000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>92100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>81000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>86100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>81300</v>
+      </c>
+      <c r="K66" s="3">
+        <v>98700</v>
+      </c>
+      <c r="L66" s="3">
         <v>113700</v>
       </c>
-      <c r="E66" s="3">
-        <v>110400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>108600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>99600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>104200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>95300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>98700</v>
-      </c>
-      <c r="K66" s="3">
-        <v>113700</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>111900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>119100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>122100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>164200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>99900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>96800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>91300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>84500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>90400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>89200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>83600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>79300</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5580,11 +5748,11 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>218000</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,80 +5854,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-42100</v>
+        <v>-39700</v>
       </c>
       <c r="E72" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-44800</v>
       </c>
-      <c r="F72" s="3">
-        <v>-41800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-44200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-46800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-46500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-44800</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-48200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-48500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-44300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-34800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-31900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-41500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-33900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-41600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-41700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-45000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-38300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-49100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-53500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5769,8 +5943,11 @@
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,80 +6210,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>342000</v>
+        <v>346200</v>
       </c>
       <c r="E76" s="3">
-        <v>339200</v>
+        <v>333800</v>
       </c>
       <c r="F76" s="3">
+        <v>333200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>344700</v>
+      </c>
+      <c r="H76" s="3">
+        <v>332500</v>
+      </c>
+      <c r="I76" s="3">
+        <v>334400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>352100</v>
+      </c>
+      <c r="K76" s="3">
+        <v>352200</v>
+      </c>
+      <c r="L76" s="3">
         <v>344600</v>
       </c>
-      <c r="G76" s="3">
-        <v>342000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>341900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>340900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>352200</v>
-      </c>
-      <c r="K76" s="3">
-        <v>344600</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>335200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>332800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>337800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>347100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>342300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>371300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>361400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>386700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>395500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>418900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>406900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>398100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>379300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-54600</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="E81" s="3">
-        <v>-3000</v>
+        <v>2600</v>
       </c>
       <c r="F81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G81" s="3">
         <v>2500</v>
       </c>
-      <c r="G81" s="3">
-        <v>2600</v>
-      </c>
       <c r="H81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,31 +6606,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,31 +7138,34 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7010,8 +7227,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,31 +7262,32 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,31 +7527,34 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,31 +8005,34 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7848,31 +8094,34 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7934,31 +8183,34 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -8018,6 +8270,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>SY</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E8" s="3">
         <v>53000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>52800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>56800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>44700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>62100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>61300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>64200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>51600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>59100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>53000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>48400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>55200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>46600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>43500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>26600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>23600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>21800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E10" s="3">
         <v>32700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>34700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>35700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>44500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>48600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>44100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>50200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>44900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>40900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>46100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>38300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>35900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>25800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E12" s="3">
         <v>5700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1263,13 +1279,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>75000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
@@ -1277,60 +1296,60 @@
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
         <v>9100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>16</v>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1343,8 +1362,8 @@
       <c r="AB14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1352,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1376,11 +1398,11 @@
         <v>1600</v>
       </c>
       <c r="J15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K15" s="3">
         <v>1700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E17" s="3">
         <v>52300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>55100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>55800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>59700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>68900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>61100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>60300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>57400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>49800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>36100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>43500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>41900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1682,124 +1714,128 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>1400</v>
       </c>
       <c r="R20" s="3">
         <v>1400</v>
       </c>
       <c r="S20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T20" s="3">
         <v>2900</v>
-      </c>
-      <c r="T20" s="3">
-        <v>2200</v>
       </c>
       <c r="U20" s="3">
         <v>2200</v>
       </c>
       <c r="V20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E21" s="3">
         <v>2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1860,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1886,8 +1925,8 @@
       <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1949,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2047,88 +2092,91 @@
         <v>300</v>
       </c>
       <c r="E24" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>-400</v>
       </c>
       <c r="G24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H24" s="3">
         <v>-1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-83300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2500</v>
       </c>
       <c r="H27" s="3">
         <v>2500</v>
       </c>
       <c r="I27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-1400</v>
       </c>
       <c r="R32" s="3">
         <v>-1400</v>
       </c>
       <c r="S32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T32" s="3">
         <v>-2900</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-2200</v>
       </c>
       <c r="U32" s="3">
         <v>-2200</v>
       </c>
       <c r="V32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>2500</v>
       </c>
       <c r="H33" s="3">
         <v>2500</v>
       </c>
       <c r="I33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>2500</v>
       </c>
       <c r="H35" s="3">
         <v>2500</v>
       </c>
       <c r="I35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,83 +3351,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E41" s="3">
         <v>66600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>62900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>62100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>60100</v>
       </c>
       <c r="H41" s="3">
         <v>60100</v>
       </c>
       <c r="I41" s="3">
+        <v>60100</v>
+      </c>
+      <c r="J41" s="3">
         <v>104600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>118800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>98600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>203300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>217500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>183900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>224100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>163300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>139800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>156900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>81400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>232000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>144600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>136200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>94000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>169200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>108000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3355,83 +3441,86 @@
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E42" s="3">
         <v>97100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>97000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>121200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>127000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>130300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>105100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>94300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>123500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>125500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>56500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>154200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>230000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>212600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>329000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>190600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>288200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>299200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>331800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>238000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>85300</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3444,83 +3533,86 @@
       <c r="AE42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E43" s="3">
         <v>21300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8200</v>
-      </c>
-      <c r="W43" s="3">
-        <v>7000</v>
       </c>
       <c r="X43" s="3">
         <v>7000</v>
       </c>
       <c r="Y43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z43" s="3">
         <v>4300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3533,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3542,44 +3637,44 @@
         <v>20800</v>
       </c>
       <c r="E44" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F44" s="3">
         <v>19700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3595,8 +3690,8 @@
       <c r="V44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3622,83 +3717,86 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E45" s="3">
         <v>31500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9600</v>
-      </c>
-      <c r="V45" s="3">
-        <v>13000</v>
       </c>
       <c r="W45" s="3">
         <v>13000</v>
       </c>
       <c r="X45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Y45" s="3">
         <v>13500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8700</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3711,83 +3809,86 @@
       <c r="AE45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>236200</v>
+      </c>
+      <c r="E46" s="3">
         <v>252100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>239200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>242200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>242800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>249200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>263000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>263100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>270200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>274000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>263300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>271600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>279900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>302900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>348900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>394800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>389200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>431900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>441900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>453900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>455300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>446200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>423400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>206300</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3800,83 +3901,86 @@
       <c r="AE46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E47" s="3">
         <v>41000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>38300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>36800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>34600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>34700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>35500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>34700</v>
-      </c>
-      <c r="N47" s="3">
-        <v>34900</v>
       </c>
       <c r="O47" s="3">
         <v>34900</v>
       </c>
       <c r="P47" s="3">
+        <v>34900</v>
+      </c>
+      <c r="Q47" s="3">
         <v>36000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>31800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>25000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>23100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2300</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3889,83 +3993,86 @@
       <c r="AE47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E48" s="3">
         <v>44700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>29700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26600</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3978,71 +4085,74 @@
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E49" s="3">
         <v>95800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>92700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>94200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>96700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>94800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>96200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>102500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>100100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>99000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>99800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>101300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>101400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>107500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4058,8 +4168,8 @@
       <c r="AB49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,83 +4361,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E52" s="3">
         <v>25800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26200</v>
       </c>
-      <c r="G52" s="3">
-        <v>32800</v>
-      </c>
       <c r="H52" s="3">
+        <v>24600</v>
+      </c>
+      <c r="I52" s="3">
         <v>21100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7500</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,83 +4545,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>374700</v>
+      </c>
+      <c r="E54" s="3">
         <v>471000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>444800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>441600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>453300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>429300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>436300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>450500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>450800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>458300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>447100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>451800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>459900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>511200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>442400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>471200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>458200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>477500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>486800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>503400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>497300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>487300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>462900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>242700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4512,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,13 +4707,14 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>16</v>
+      <c r="D57" s="3">
+        <v>2800</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>16</v>
@@ -4592,24 +4722,24 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -4617,13 +4747,13 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
       </c>
       <c r="Q57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
@@ -4632,28 +4762,28 @@
         <v>300</v>
       </c>
       <c r="T57" s="3">
+        <v>300</v>
+      </c>
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
-      </c>
-      <c r="V57" s="3">
-        <v>400</v>
       </c>
       <c r="W57" s="3">
         <v>400</v>
       </c>
       <c r="X57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>16</v>
+      <c r="AA57" s="3">
+        <v>0</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>16</v>
@@ -4667,43 +4797,46 @@
       <c r="AE57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E58" s="3">
         <v>18500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4756,83 +4889,86 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E59" s="3">
         <v>21200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>75000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>94900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>91400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>96800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>98300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>84400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>82800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>79100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>73200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>64100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>68700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>61900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>57400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4845,83 +4981,86 @@
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E60" s="3">
         <v>86700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>76500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>81200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>75900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>94900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>91400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>98400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>135900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>84700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>83100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>79500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>74400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>73600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>64500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>71800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>69200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>62600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>57400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4934,35 +5073,38 @@
       <c r="AE60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E61" s="3">
         <v>17800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5023,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5035,71 +5180,71 @@
         <v>200</v>
       </c>
       <c r="F62" s="3">
+        <v>200</v>
+      </c>
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>20000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,83 +5533,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>106400</v>
+      </c>
+      <c r="E66" s="3">
         <v>107700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>94500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>92000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>92100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>81000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>81300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>113700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>111900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>119100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>122100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>164200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>100200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>99900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>96800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>90700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>91300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>84500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>90400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>89200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>83600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>79300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5468,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5751,11 +5918,11 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>218000</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,83 +6027,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-121400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-41800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-43000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-48000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-44800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-48200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-48500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-44300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-34800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-32800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-41500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-33900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-41600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-41700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-45000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-38300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-49100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-53500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-57700</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5946,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,83 +6395,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E76" s="3">
         <v>346200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>333800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>333200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>344700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>332500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>334400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>352100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>352200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>344600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>335200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>332800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>337800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>347100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>342300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>371300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>361400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>386700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>395500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>418900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>406900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>398100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>379300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-54600</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6302,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>2500</v>
       </c>
       <c r="H81" s="3">
         <v>2500</v>
       </c>
       <c r="I81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6633,8 +6831,8 @@
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7167,8 +7383,8 @@
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -7230,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7289,8 +7509,8 @@
       <c r="J91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -7352,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7556,8 +7785,8 @@
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -7619,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,8 +7911,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8034,8 +8279,8 @@
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8097,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,8 +8371,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8186,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8212,8 +8463,8 @@
       <c r="J102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -8273,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>SY</t>
   </si>
@@ -656,416 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F8" s="3">
         <v>50600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>53000</v>
       </c>
-      <c r="F8" s="3">
-        <v>56100</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
         <v>44100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>55100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>52800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>56800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>45100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>45800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>44700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>42700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>41700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>62100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>61300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>64200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>51600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>59100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>53000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>48400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>28800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>55200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>46600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>43500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>31400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>26600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>23600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>21800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>16300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F9" s="3">
         <v>21000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>20300</v>
       </c>
-      <c r="F9" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3">
         <v>16200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>19400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>19500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>20700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>16600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>12400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>13000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>14800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>17500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>12700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>8400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>7500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>8900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>8100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>7500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>6800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>9000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>8300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>7600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>5500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>3400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>3000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F10" s="3">
         <v>29600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>32700</v>
       </c>
-      <c r="F10" s="3">
-        <v>34700</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
         <v>27800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>35700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>33300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>36100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>28600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>33400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>31700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>28300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>26900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>44500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>48600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>55900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>44100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>50200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>44900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>40900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>22000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>46100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>38300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>35900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>25800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>22000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>20200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>18800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>14200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1124,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F12" s="3">
         <v>5900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>5700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>6300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>6900</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="O12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
-        <v>8100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>5800</v>
-      </c>
-      <c r="M12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>8700</v>
-      </c>
-      <c r="O12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>9300</v>
       </c>
       <c r="Q12" s="3">
         <v>11000</v>
       </c>
       <c r="R12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="T12" s="3">
         <v>10300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>10000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>9900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>9300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>6800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>8400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>6100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>7900</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>4800</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>3800</v>
       </c>
       <c r="AC12" s="3">
         <v>4800</v>
       </c>
       <c r="AD12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF12" s="3">
         <v>3000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,80 +1316,86 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>75000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R14" s="3">
         <v>9100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>2500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1365,22 +1405,28 @@
       <c r="AC14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>1600</v>
@@ -1392,7 +1438,7 @@
         <v>1600</v>
       </c>
       <c r="H15" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>1600</v>
@@ -1401,14 +1447,14 @@
         <v>1600</v>
       </c>
       <c r="K15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M15" s="3">
         <v>1700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1512,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1549,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
+        <v>46900</v>
+      </c>
+      <c r="F17" s="3">
         <v>58700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>52300</v>
       </c>
-      <c r="F17" s="3">
-        <v>55100</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
         <v>49200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>55800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>53100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>59700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>50000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>42400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>46800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>48500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>52600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>68900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>61100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>56000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>60300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>55000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>57400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>49800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>36100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>43900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>43500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>41900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>25600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>21700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>26700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>20700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>12100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="F18" s="3">
-        <v>900</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-10800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>8200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-8600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-4500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-7300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>11200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>3100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>5800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>4900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>4300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,133 +1781,141 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
-        <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>700</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>1300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>800</v>
       </c>
       <c r="Q20" s="3">
         <v>1200</v>
       </c>
       <c r="R20" s="3">
+        <v>800</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>2200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-8600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2800</v>
       </c>
-      <c r="F21" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1899,8 +1973,14 @@
       <c r="AF21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1928,11 +2008,11 @@
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1991,192 +2071,210 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-83000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>9600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>7100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-6300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>15200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>5300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>6100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>8100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>6000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>4700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="J24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S24" s="3">
+        <v>600</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="X24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="V24" s="3">
-        <v>400</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="X24" s="3">
-        <v>4500</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>200</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2365,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-83300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>8000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-6600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-5700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>10800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>4900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>7000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>5900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>4400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-83200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2900</v>
       </c>
-      <c r="F27" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>4400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>8200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>5400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-5700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>10800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>4900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2659,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2757,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2855,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2953,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-700</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-800</v>
       </c>
       <c r="Q32" s="3">
         <v>-1200</v>
       </c>
       <c r="R32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-83200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2900</v>
       </c>
-      <c r="F33" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>8200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>5400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-5700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>10800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>4900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3247,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-83200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2900</v>
       </c>
-      <c r="F35" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>8200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>5400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-5700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>10800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>4900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3488,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,89 +3524,91 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3">
+        <v>61300</v>
+      </c>
+      <c r="F41" s="3">
         <v>80500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>66600</v>
       </c>
-      <c r="F41" s="3">
-        <v>62900</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3">
         <v>62100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>60100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>60100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>104600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>118800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>97900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>98600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>203300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>217500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>183900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>224100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>163300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>139800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>156900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>81400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>232000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>144600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>136200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>94000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>169200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>108000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3444,89 +3618,95 @@
       <c r="AF41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>79300</v>
+      </c>
+      <c r="F42" s="3">
         <v>82100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>97100</v>
       </c>
-      <c r="F42" s="3">
-        <v>97000</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>121200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>127000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>130300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>105100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>94300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>123500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>125500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>15300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>15400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>56500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>33300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>154200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>230000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>212600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>329000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>190600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>288200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>299200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>331800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>238000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>85300</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3536,89 +3716,95 @@
       <c r="AF42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F43" s="3">
         <v>31000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>21300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
+        <v>13800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>28300</v>
+      </c>
+      <c r="K43" s="3">
+        <v>15800</v>
+      </c>
+      <c r="L43" s="3">
+        <v>13100</v>
+      </c>
+      <c r="M43" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N43" s="3">
+        <v>11900</v>
+      </c>
+      <c r="O43" s="3">
+        <v>12400</v>
+      </c>
+      <c r="P43" s="3">
+        <v>11700</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="R43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="S43" s="3">
         <v>15500</v>
       </c>
-      <c r="G43" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H43" s="3">
-        <v>28300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>15800</v>
-      </c>
-      <c r="J43" s="3">
-        <v>13100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>11600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>11900</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="T43" s="3">
+        <v>14000</v>
+      </c>
+      <c r="U43" s="3">
         <v>12400</v>
       </c>
-      <c r="N43" s="3">
-        <v>11700</v>
-      </c>
-      <c r="O43" s="3">
-        <v>12200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>12100</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>15500</v>
-      </c>
-      <c r="R43" s="3">
-        <v>14000</v>
-      </c>
-      <c r="S43" s="3">
-        <v>12400</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>10700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>10300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>9800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>8200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>7000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>7000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3628,59 +3814,65 @@
       <c r="AF43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F44" s="3">
         <v>20800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>20800</v>
       </c>
-      <c r="F44" s="3">
-        <v>19700</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3">
         <v>17500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>16800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>15800</v>
-      </c>
-      <c r="J44" s="3">
-        <v>17000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>17400</v>
       </c>
       <c r="L44" s="3">
         <v>17000</v>
       </c>
       <c r="M44" s="3">
+        <v>17400</v>
+      </c>
+      <c r="N44" s="3">
+        <v>17000</v>
+      </c>
+      <c r="O44" s="3">
         <v>14500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>13100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>12400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>12700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>13000</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3693,11 +3885,11 @@
       <c r="W44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -3720,89 +3912,95 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F45" s="3">
         <v>7200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>31500</v>
       </c>
-      <c r="F45" s="3">
-        <v>32700</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>24600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>25000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>21000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>18600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>20000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>22900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>19800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>14100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>14800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>17100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>17500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>12600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>9100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>11300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>9600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>13000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>13000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>13500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>11900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>8700</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3812,89 +4010,95 @@
       <c r="AF45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3">
+        <v>222800</v>
+      </c>
+      <c r="F46" s="3">
         <v>236200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>252100</v>
       </c>
-      <c r="F46" s="3">
-        <v>239200</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="3">
         <v>242200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>242800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>249200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>263000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>263100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>270200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>274000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>263300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>271600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>279900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>302900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>348900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>394800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>389200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>431900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>441900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>453900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>455300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>446200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>423400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>206300</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3904,89 +4108,95 @@
       <c r="AF46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3">
+        <v>38200</v>
+      </c>
+      <c r="F47" s="3">
         <v>38400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>41000</v>
       </c>
-      <c r="F47" s="3">
-        <v>38300</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3">
         <v>35500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>36800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>34600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>34700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>35500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>32100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>32300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>34700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>34900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>34900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>36000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>31800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>25000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>23100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>6100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>7000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>7100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>5600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>4900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3996,89 +4206,95 @@
       <c r="AF47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3">
+        <v>48300</v>
+      </c>
+      <c r="F48" s="3">
         <v>43600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>44700</v>
       </c>
-      <c r="F48" s="3">
-        <v>38100</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3">
         <v>32600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>33200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>20400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>22500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>24600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>25800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>28100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>29400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>30400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>32400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>18600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>20200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>20900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>23600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>24600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>27400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>27200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>28800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>29700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>26600</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4088,77 +4304,83 @@
       <c r="AF48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F49" s="3">
         <v>17400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>95800</v>
       </c>
-      <c r="F49" s="3">
-        <v>92700</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="3">
         <v>94200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>96700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>94800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>96200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>102500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>100100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>99000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>99800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>101300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>101400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>107500</v>
-      </c>
-      <c r="R49" s="3">
-        <v>15100</v>
-      </c>
-      <c r="S49" s="3">
-        <v>15300</v>
       </c>
       <c r="T49" s="3">
         <v>15100</v>
       </c>
       <c r="U49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="V49" s="3">
+        <v>15100</v>
+      </c>
+      <c r="W49" s="3">
         <v>6100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>6200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>6900</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4171,17 +4393,23 @@
       <c r="AC49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4500,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,89 +4598,95 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F52" s="3">
         <v>17600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>25800</v>
       </c>
-      <c r="F52" s="3">
-        <v>25300</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3">
         <v>26200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>24600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>21100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>11000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>15400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>23100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>27200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>21200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>14600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>13200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>32400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>28100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>15900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>9900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>9800</v>
-      </c>
-      <c r="V52" s="3">
-        <v>7700</v>
-      </c>
-      <c r="W52" s="3">
-        <v>8200</v>
       </c>
       <c r="X52" s="3">
         <v>7700</v>
       </c>
       <c r="Y52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AA52" s="3">
         <v>6600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>4900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>7500</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4456,8 +4696,14 @@
       <c r="AF52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,89 +4794,95 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="3">
+        <v>364400</v>
+      </c>
+      <c r="F54" s="3">
         <v>374700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>471000</v>
       </c>
-      <c r="F54" s="3">
-        <v>444800</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
         <v>441600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>453300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>429300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>436300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>450500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>450800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>458300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>447100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>451800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>459900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>511200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>442400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>471200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>458200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>477500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>486800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>503400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>497300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>487300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>462900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>242700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4640,8 +4892,14 @@
       <c r="AF54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4932,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,64 +4968,66 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
-      </c>
-      <c r="R57" s="3">
-        <v>300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>300</v>
       </c>
       <c r="T57" s="3">
         <v>300</v>
       </c>
       <c r="U57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
@@ -4774,22 +5036,22 @@
         <v>400</v>
       </c>
       <c r="X57" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>700</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>16</v>
+      <c r="AC57" s="3">
+        <v>0</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>16</v>
@@ -4800,49 +5062,55 @@
       <c r="AF57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F58" s="3">
         <v>15700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>18500</v>
       </c>
-      <c r="F58" s="3">
-        <v>9200</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="3">
         <v>7800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>8400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>7400</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4892,89 +5160,95 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F59" s="3">
         <v>38900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>21200</v>
       </c>
-      <c r="F59" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="3">
         <v>27400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>40700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>24200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>23100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>24900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>75000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>94900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>91400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>96800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>98300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>135800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>84400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>82800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>79100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>74000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>73200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>64100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>71400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>68700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>61900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>57400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4984,89 +5258,95 @@
       <c r="AF59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3">
+        <v>80900</v>
+      </c>
+      <c r="F60" s="3">
         <v>86300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>86700</v>
       </c>
-      <c r="F60" s="3">
-        <v>75600</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="3">
         <v>75300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>76200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>76500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>81200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>75400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>75900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>94900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>91400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>96800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>98400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>135900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>84700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>83100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>79500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>74400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>73600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>64500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>71800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>69200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>62600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>57400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5076,41 +5356,47 @@
       <c r="AF60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F61" s="3">
         <v>17200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>17800</v>
       </c>
-      <c r="F61" s="3">
-        <v>15800</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>13200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>12200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5168,13 +5454,19 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E62" s="3">
         <v>200</v>
@@ -5183,74 +5475,74 @@
         <v>200</v>
       </c>
       <c r="G62" s="3">
+        <v>200</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>7300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>10800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>12400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>13900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>14600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>12500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>13700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>14100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>16300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>17800</v>
-      </c>
-      <c r="W62" s="3">
-        <v>20000</v>
-      </c>
-      <c r="X62" s="3">
-        <v>18600</v>
       </c>
       <c r="Y62" s="3">
         <v>20000</v>
       </c>
       <c r="Z62" s="3">
+        <v>18600</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AB62" s="3">
         <v>21000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>21900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5260,8 +5552,14 @@
       <c r="AF62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5650,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5748,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,89 +5846,95 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3">
+        <v>102500</v>
+      </c>
+      <c r="F66" s="3">
         <v>106400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>107700</v>
       </c>
-      <c r="F66" s="3">
-        <v>94500</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="3">
         <v>92000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>92100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>81000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>86100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>81300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>98700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>113700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>111900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>119100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>122100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>164200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>100200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>99900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>96800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>90700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>91300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>84500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>90400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>89200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>83600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>79300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5628,8 +5944,14 @@
       <c r="AF66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5984,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6078,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6176,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5921,14 +6257,14 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>218000</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6274,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,89 +6372,95 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-126600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-121400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-39700</v>
       </c>
-      <c r="F72" s="3">
-        <v>-41100</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3">
         <v>-44000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-41800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-43000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-45800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-48000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-44800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-48200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-48500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-44300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-31900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-32800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-41500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-33900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-41600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-41700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-45000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-38300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-49100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-53500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-57700</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6122,8 +6470,14 @@
       <c r="AF72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6568,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6666,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,89 +6764,95 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3">
+        <v>245500</v>
+      </c>
+      <c r="F76" s="3">
         <v>252000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>346200</v>
       </c>
-      <c r="F76" s="3">
-        <v>333800</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="3">
         <v>333200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>344700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>332500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>334400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>352100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>352200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>344600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>335200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>332800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>337800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>347100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>342300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>371300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>361400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>386700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>395500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>418900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>406900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>398100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>379300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-54600</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6490,8 +6862,14 @@
       <c r="AF76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6960,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-83200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2900</v>
       </c>
-      <c r="F81" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>8200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>5400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-5700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>10800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>4900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7201,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6834,11 +7232,11 @@
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6897,8 +7295,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7393,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7491,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7589,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7687,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7785,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7386,11 +7820,11 @@
       <c r="K89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -7449,8 +7883,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7923,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7512,11 +7954,11 @@
       <c r="K91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7575,8 +8017,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8115,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8213,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7788,11 +8248,11 @@
       <c r="K94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -7851,8 +8311,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8351,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7914,11 +8382,11 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7977,8 +8445,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8543,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8641,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8739,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8282,11 +8774,11 @@
       <c r="K100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -8345,8 +8837,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8374,11 +8872,11 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8437,8 +8935,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8466,11 +8970,11 @@
       <c r="K102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -8527,6 +9031,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>
